--- a/excel_routes/route_CAI_RUH_threats.xlsx
+++ b/excel_routes/route_CAI_RUH_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K246" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K270" s="2" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K313" s="2" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K314" s="2" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K315" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="J316" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K317" s="2" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K318" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K319" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K320" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K321" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K322" s="2" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="J325" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K327" s="2" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K329" s="2" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K336" s="2" t="inlineStr">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K337" s="2" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K338" s="2" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="J340" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K340" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K341" s="2" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K342" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K343" s="2" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="J344" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K344" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K345" s="2" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K346" s="2" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K347" s="2" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K348" s="2" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="J349" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K349" s="2" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K350" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K351" s="2" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K352" s="2" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K353" s="2" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K354" s="2" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K355" s="2" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K356" s="2" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K357" s="2" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K358" s="2" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K359" s="2" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K360" s="2" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K361" s="2" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K362" s="2" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K363" s="2" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K364" s="2" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K365" s="2" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K366" s="2" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K367" s="2" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="J368" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K368" s="2" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="J369" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K369" s="2" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K370" s="2" t="inlineStr">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K371" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="J372" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K372" s="2" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="J373" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K373" s="2" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="J374" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K374" s="2" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="J375" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K375" s="2" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="J376" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K376" s="2" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="J377" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K377" s="2" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="J378" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K378" s="2" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="J379" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K379" s="2" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="J380" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K380" s="2" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="J381" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K381" s="2" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="J382" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K382" s="2" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K383" s="2" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K384" s="2" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K385" s="2" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K386" s="2" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K387" s="2" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K388" s="2" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K389" s="2" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K390" s="2" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K391" s="2" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="J392" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K392" s="2" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="J393" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K393" s="2" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="J394" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K394" s="2" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="J395" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K395" s="2" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="J396" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K396" s="2" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="J397" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K397" s="2" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="J398" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K398" s="2" t="inlineStr">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K399" s="2" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="J400" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K400" s="2" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K401" s="2" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="J402" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K402" s="2" t="inlineStr">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="J403" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K403" s="2" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="J404" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K404" s="2" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="J405" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K405" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="J406" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K406" s="2" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="J407" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K407" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="J408" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K408" s="2" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="J409" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K409" s="2" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="J410" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K410" s="2" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="J411" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K411" s="2" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K412" s="2" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="J413" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K413" s="2" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K414" s="2" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K415" s="2" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K416" s="2" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K417" s="2" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="J418" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K418" s="2" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="J419" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K419" s="2" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="J420" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K420" s="2" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K421" s="2" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K422" s="2" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="J423" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K423" s="2" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K424" s="2" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K425" s="2" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K426" s="2" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K427" s="2" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K428" s="2" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="J429" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K429" s="2" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K430" s="2" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K431" s="2" t="inlineStr">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K432" s="2" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K433" s="2" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K434" s="2" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K435" s="2" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K436" s="2" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K437" s="2" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K438" s="2" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K439" s="2" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K440" s="2" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K441" s="2" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K442" s="2" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K443" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K444" s="2" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K445" s="2" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K446" s="2" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K447" s="2" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K448" s="2" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K449" s="2" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K450" s="2" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K451" s="2" t="inlineStr">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K452" s="2" t="inlineStr">
@@ -20869,7 +20869,7 @@
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K453" s="2" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K454" s="2" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K455" s="2" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K456" s="2" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K457" s="2" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K458" s="2" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K459" s="2" t="inlineStr">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K460" s="2" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K461" s="2" t="inlineStr">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K462" s="2" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K463" s="2" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K464" s="2" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K465" s="2" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K466" s="2" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="J467" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K467" s="2" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="J468" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K468" s="2" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K469" s="2" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K470" s="2" t="inlineStr">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K471" s="2" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K472" s="2" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K473" s="2" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K474" s="2" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K475" s="2" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K476" s="2" t="inlineStr">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K477" s="2" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K478" s="2" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K479" s="2" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K480" s="2" t="inlineStr">
@@ -22129,7 +22129,7 @@
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K481" s="2" t="inlineStr">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K482" s="2" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K483" s="2" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K484" s="2" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K485" s="2" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K486" s="2" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K487" s="2" t="inlineStr">
@@ -22444,7 +22444,7 @@
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K488" s="2" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K489" s="2" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="J490" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K490" s="2" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K491" s="2" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K492" s="2" t="inlineStr">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="J493" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K493" s="2" t="inlineStr">
@@ -22714,7 +22714,7 @@
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K494" s="2" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K495" s="2" t="inlineStr">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K496" s="2" t="inlineStr">
@@ -22849,7 +22849,7 @@
       </c>
       <c r="J497" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K497" s="2" t="inlineStr">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="J498" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K498" s="2" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K499" s="2" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="J500" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K500" s="2" t="inlineStr">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K501" s="2" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K502" s="2" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="J503" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K503" s="2" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K504" s="2" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K505" s="2" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="J506" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K506" s="2" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K507" s="2" t="inlineStr">
@@ -23344,7 +23344,7 @@
       </c>
       <c r="J508" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K508" s="2" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="J509" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K509" s="2" t="inlineStr">
@@ -23434,7 +23434,7 @@
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K510" s="2" t="inlineStr">
@@ -23479,7 +23479,7 @@
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K511" s="2" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="J512" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K512" s="2" t="inlineStr">
@@ -23569,7 +23569,7 @@
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K513" s="2" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="J514" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K514" s="2" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K515" s="2" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K516" s="2" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K517" s="2" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="J518" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K518" s="2" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="J519" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K519" s="2" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="J520" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K520" s="2" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K521" s="2" t="inlineStr">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K522" s="2" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="J523" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K523" s="2" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="J524" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K524" s="2" t="inlineStr">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="J525" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K525" s="2" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="J526" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K526" s="2" t="inlineStr">
@@ -24199,7 +24199,7 @@
       </c>
       <c r="J527" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K527" s="2" t="inlineStr">
@@ -24244,7 +24244,7 @@
       </c>
       <c r="J528" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K528" s="2" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K529" s="2" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="J530" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K530" s="2" t="inlineStr">
@@ -24379,7 +24379,7 @@
       </c>
       <c r="J531" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K531" s="2" t="inlineStr">
@@ -24424,7 +24424,7 @@
       </c>
       <c r="J532" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K532" s="2" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="J533" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K533" s="2" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="J534" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K534" s="2" t="inlineStr">
@@ -24559,7 +24559,7 @@
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K535" s="2" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="J536" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K536" s="2" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K537" s="2" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K538" s="2" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="J539" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K539" s="2" t="inlineStr">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="J540" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K540" s="2" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K541" s="2" t="inlineStr">
@@ -24874,7 +24874,7 @@
       </c>
       <c r="J542" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K542" s="2" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="J543" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K543" s="2" t="inlineStr">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="J544" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K544" s="2" t="inlineStr">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="J545" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K545" s="2" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="J546" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K546" s="2" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="J547" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K547" s="2" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="J548" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K548" s="2" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="J549" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K549" s="2" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K550" s="2" t="inlineStr">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="J551" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K551" s="2" t="inlineStr">
@@ -25324,7 +25324,7 @@
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K552" s="2" t="inlineStr">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K553" s="2" t="inlineStr">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="J554" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K554" s="2" t="inlineStr">
@@ -25459,7 +25459,7 @@
       </c>
       <c r="J555" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K555" s="2" t="inlineStr">
@@ -25504,7 +25504,7 @@
       </c>
       <c r="J556" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K556" s="2" t="inlineStr">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="J557" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K557" s="2" t="inlineStr">
@@ -25594,7 +25594,7 @@
       </c>
       <c r="J558" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K558" s="2" t="inlineStr">
@@ -25639,7 +25639,7 @@
       </c>
       <c r="J559" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K559" s="2" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="J560" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K560" s="2" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="J561" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K561" s="2" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="J562" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K562" s="2" t="inlineStr">
@@ -25819,7 +25819,7 @@
       </c>
       <c r="J563" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K563" s="2" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="J564" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K564" s="2" t="inlineStr">
@@ -25909,7 +25909,7 @@
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K565" s="2" t="inlineStr">
@@ -25954,7 +25954,7 @@
       </c>
       <c r="J566" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K566" s="2" t="inlineStr">
@@ -25999,7 +25999,7 @@
       </c>
       <c r="J567" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K567" s="2" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="J568" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K568" s="2" t="inlineStr">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="J569" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K569" s="2" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="J570" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K570" s="2" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="J571" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K571" s="2" t="inlineStr">
@@ -26224,7 +26224,7 @@
       </c>
       <c r="J572" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K572" s="2" t="inlineStr">
@@ -26269,7 +26269,7 @@
       </c>
       <c r="J573" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K573" s="2" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="J574" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K574" s="2" t="inlineStr">
@@ -26359,7 +26359,7 @@
       </c>
       <c r="J575" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K575" s="2" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="J576" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K576" s="2" t="inlineStr">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="J577" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K577" s="2" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="J578" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K578" s="2" t="inlineStr">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="J579" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K579" s="2" t="inlineStr">
@@ -26584,7 +26584,7 @@
       </c>
       <c r="J580" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K580" s="2" t="inlineStr">
@@ -26629,7 +26629,7 @@
       </c>
       <c r="J581" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K581" s="2" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K582" s="2" t="inlineStr">
@@ -26719,7 +26719,7 @@
       </c>
       <c r="J583" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K583" s="2" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="J584" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K584" s="2" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="J585" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K585" s="2" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K586" s="2" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K587" s="2" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="J588" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K588" s="2" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K589" s="2" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="J590" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K590" s="2" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="J591" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K591" s="2" t="inlineStr">
@@ -27124,7 +27124,7 @@
       </c>
       <c r="J592" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K592" s="2" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="J593" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K593" s="2" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="J594" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K594" s="2" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K595" s="2" t="inlineStr">
@@ -27304,7 +27304,7 @@
       </c>
       <c r="J596" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K596" s="2" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="J597" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K597" s="2" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="J598" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K598" s="2" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="J599" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K599" s="2" t="inlineStr">
@@ -27484,7 +27484,7 @@
       </c>
       <c r="J600" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K600" s="2" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="J601" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K601" s="2" t="inlineStr">
@@ -27574,7 +27574,7 @@
       </c>
       <c r="J602" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K602" s="2" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="J603" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K603" s="2" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="J604" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K604" s="2" t="inlineStr">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="J605" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K605" s="2" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="J606" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K606" s="2" t="inlineStr">
@@ -27799,7 +27799,7 @@
       </c>
       <c r="J607" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K607" s="2" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="J608" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K608" s="2" t="inlineStr">
@@ -27889,7 +27889,7 @@
       </c>
       <c r="J609" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K609" s="2" t="inlineStr">
@@ -27934,7 +27934,7 @@
       </c>
       <c r="J610" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K610" s="2" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="J611" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K611" s="2" t="inlineStr">
@@ -28024,7 +28024,7 @@
       </c>
       <c r="J612" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K612" s="2" t="inlineStr">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="J613" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K613" s="2" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="J614" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K614" s="2" t="inlineStr">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="J615" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K615" s="2" t="inlineStr">
@@ -28204,7 +28204,7 @@
       </c>
       <c r="J616" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K616" s="2" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="J617" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K617" s="2" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="J618" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K618" s="2" t="inlineStr">
@@ -28339,7 +28339,7 @@
       </c>
       <c r="J619" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K619" s="2" t="inlineStr">
@@ -28384,7 +28384,7 @@
       </c>
       <c r="J620" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K620" s="2" t="inlineStr">
@@ -28429,7 +28429,7 @@
       </c>
       <c r="J621" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K621" s="2" t="inlineStr">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K622" s="2" t="inlineStr">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K623" s="2" t="inlineStr">
@@ -28564,7 +28564,7 @@
       </c>
       <c r="J624" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K624" s="2" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K625" s="2" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K626" s="2" t="inlineStr">
@@ -28699,7 +28699,7 @@
       </c>
       <c r="J627" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K627" s="2" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="J628" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K628" s="2" t="inlineStr">
@@ -28789,7 +28789,7 @@
       </c>
       <c r="J629" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K629" s="2" t="inlineStr">
@@ -28834,7 +28834,7 @@
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K630" s="2" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K631" s="2" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="J632" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K632" s="2" t="inlineStr">
@@ -28969,7 +28969,7 @@
       </c>
       <c r="J633" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K633" s="2" t="inlineStr">
@@ -29014,7 +29014,7 @@
       </c>
       <c r="J634" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K634" s="2" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="J635" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K635" s="2" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="J636" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K636" s="2" t="inlineStr">
@@ -29149,7 +29149,7 @@
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K637" s="2" t="inlineStr">
@@ -29194,7 +29194,7 @@
       </c>
       <c r="J638" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K638" s="2" t="inlineStr">
@@ -29239,7 +29239,7 @@
       </c>
       <c r="J639" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K639" s="2" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="J640" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K640" s="2" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="J641" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K641" s="2" t="inlineStr">
@@ -29374,7 +29374,7 @@
       </c>
       <c r="J642" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K642" s="2" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="J643" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K643" s="2" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="J644" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K644" s="2" t="inlineStr">
@@ -29509,7 +29509,7 @@
       </c>
       <c r="J645" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K645" s="2" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K646" s="2" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="J647" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K647" s="2" t="inlineStr">
@@ -29644,7 +29644,7 @@
       </c>
       <c r="J648" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K648" s="2" t="inlineStr">
@@ -29689,7 +29689,7 @@
       </c>
       <c r="J649" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K649" s="2" t="inlineStr">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="J650" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K650" s="2" t="inlineStr">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="J651" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K651" s="2" t="inlineStr">
@@ -29824,7 +29824,7 @@
       </c>
       <c r="J652" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K652" s="2" t="inlineStr">
@@ -29869,7 +29869,7 @@
       </c>
       <c r="J653" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K653" s="2" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="J654" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K654" s="2" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="J655" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K655" s="2" t="inlineStr">
@@ -30004,7 +30004,7 @@
       </c>
       <c r="J656" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K656" s="2" t="inlineStr">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="J657" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K657" s="2" t="inlineStr">
@@ -30094,7 +30094,7 @@
       </c>
       <c r="J658" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K658" s="2" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="J659" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K659" s="2" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="J660" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K660" s="2" t="inlineStr">
@@ -30229,7 +30229,7 @@
       </c>
       <c r="J661" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K661" s="2" t="inlineStr">
@@ -30274,7 +30274,7 @@
       </c>
       <c r="J662" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K662" s="2" t="inlineStr">
@@ -30319,7 +30319,7 @@
       </c>
       <c r="J663" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K663" s="2" t="inlineStr">
@@ -30364,7 +30364,7 @@
       </c>
       <c r="J664" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K664" s="2" t="inlineStr">
@@ -30409,7 +30409,7 @@
       </c>
       <c r="J665" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K665" s="2" t="inlineStr">
@@ -30454,7 +30454,7 @@
       </c>
       <c r="J666" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K666" s="2" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="J667" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K667" s="2" t="inlineStr">
@@ -30544,7 +30544,7 @@
       </c>
       <c r="J668" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K668" s="2" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="J669" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K669" s="2" t="inlineStr">
@@ -30634,7 +30634,7 @@
       </c>
       <c r="J670" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K670" s="2" t="inlineStr">
@@ -30679,7 +30679,7 @@
       </c>
       <c r="J671" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K671" s="2" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="J672" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K672" s="2" t="inlineStr">
@@ -30769,7 +30769,7 @@
       </c>
       <c r="J673" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K673" s="2" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="J674" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K674" s="2" t="inlineStr">
@@ -30859,7 +30859,7 @@
       </c>
       <c r="J675" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K675" s="2" t="inlineStr">
@@ -30904,7 +30904,7 @@
       </c>
       <c r="J676" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K676" s="2" t="inlineStr">
@@ -30949,7 +30949,7 @@
       </c>
       <c r="J677" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K677" s="2" t="inlineStr">
@@ -30994,7 +30994,7 @@
       </c>
       <c r="J678" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K678" s="2" t="inlineStr">
@@ -31039,7 +31039,7 @@
       </c>
       <c r="J679" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K679" s="2" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="J680" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K680" s="2" t="inlineStr">
@@ -31129,7 +31129,7 @@
       </c>
       <c r="J681" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K681" s="2" t="inlineStr">
@@ -31174,7 +31174,7 @@
       </c>
       <c r="J682" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K682" s="2" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="J683" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K683" s="2" t="inlineStr">
@@ -31264,7 +31264,7 @@
       </c>
       <c r="J684" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K684" s="2" t="inlineStr">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="J685" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K685" s="2" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="J686" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K686" s="2" t="inlineStr">
@@ -31399,7 +31399,7 @@
       </c>
       <c r="J687" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K687" s="2" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="J688" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K688" s="2" t="inlineStr">
@@ -31489,7 +31489,7 @@
       </c>
       <c r="J689" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K689" s="2" t="inlineStr">
@@ -31534,7 +31534,7 @@
       </c>
       <c r="J690" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K690" s="2" t="inlineStr">
@@ -31579,7 +31579,7 @@
       </c>
       <c r="J691" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K691" s="2" t="inlineStr">
@@ -31624,7 +31624,7 @@
       </c>
       <c r="J692" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K692" s="2" t="inlineStr">
@@ -31669,7 +31669,7 @@
       </c>
       <c r="J693" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K693" s="2" t="inlineStr">
@@ -31714,7 +31714,7 @@
       </c>
       <c r="J694" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K694" s="2" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="J695" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K695" s="2" t="inlineStr">
@@ -31804,7 +31804,7 @@
       </c>
       <c r="J696" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K696" s="2" t="inlineStr">
@@ -31849,7 +31849,7 @@
       </c>
       <c r="J697" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K697" s="2" t="inlineStr">
@@ -31894,7 +31894,7 @@
       </c>
       <c r="J698" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K698" s="2" t="inlineStr">
@@ -31939,7 +31939,7 @@
       </c>
       <c r="J699" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K699" s="2" t="inlineStr">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="J700" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K700" s="2" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="J701" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K701" s="2" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="J702" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K702" s="2" t="inlineStr">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="J703" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K703" s="2" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="J704" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K704" s="2" t="inlineStr">
@@ -32209,7 +32209,7 @@
       </c>
       <c r="J705" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K705" s="2" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="J706" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K706" s="2" t="inlineStr">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="J707" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K707" s="2" t="inlineStr">
@@ -32344,7 +32344,7 @@
       </c>
       <c r="J708" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K708" s="2" t="inlineStr">
@@ -32389,7 +32389,7 @@
       </c>
       <c r="J709" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K709" s="2" t="inlineStr">
@@ -32434,7 +32434,7 @@
       </c>
       <c r="J710" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K710" s="2" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="J711" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K711" s="2" t="inlineStr">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="J712" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K712" s="2" t="inlineStr">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="J713" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K713" s="2" t="inlineStr">
@@ -32614,7 +32614,7 @@
       </c>
       <c r="J714" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K714" s="2" t="inlineStr">
@@ -32659,7 +32659,7 @@
       </c>
       <c r="J715" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K715" s="2" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="J716" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K716" s="2" t="inlineStr">
@@ -32749,7 +32749,7 @@
       </c>
       <c r="J717" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K717" s="2" t="inlineStr">
@@ -32794,7 +32794,7 @@
       </c>
       <c r="J718" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K718" s="2" t="inlineStr">
@@ -32839,7 +32839,7 @@
       </c>
       <c r="J719" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K719" s="2" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="J720" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K720" s="2" t="inlineStr">
@@ -32929,7 +32929,7 @@
       </c>
       <c r="J721" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K721" s="2" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="J722" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K722" s="2" t="inlineStr">
@@ -33019,7 +33019,7 @@
       </c>
       <c r="J723" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K723" s="2" t="inlineStr">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="J724" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K724" s="2" t="inlineStr">
@@ -33109,7 +33109,7 @@
       </c>
       <c r="J725" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K725" s="2" t="inlineStr">
@@ -33154,7 +33154,7 @@
       </c>
       <c r="J726" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K726" s="2" t="inlineStr">
@@ -33199,7 +33199,7 @@
       </c>
       <c r="J727" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K727" s="2" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="J728" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K728" s="2" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="J729" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K729" s="2" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="J730" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K730" s="2" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="J731" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K731" s="2" t="inlineStr">
@@ -33424,7 +33424,7 @@
       </c>
       <c r="J732" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K732" s="2" t="inlineStr">
@@ -33469,7 +33469,7 @@
       </c>
       <c r="J733" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K733" s="2" t="inlineStr">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="J734" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K734" s="2" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="J735" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K735" s="2" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="J736" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K736" s="2" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="J737" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K737" s="2" t="inlineStr">
@@ -33694,7 +33694,7 @@
       </c>
       <c r="J738" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K738" s="2" t="inlineStr">
@@ -33739,7 +33739,7 @@
       </c>
       <c r="J739" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K739" s="2" t="inlineStr">
@@ -33784,7 +33784,7 @@
       </c>
       <c r="J740" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K740" s="2" t="inlineStr">
@@ -33829,7 +33829,7 @@
       </c>
       <c r="J741" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K741" s="2" t="inlineStr">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="J742" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K742" s="2" t="inlineStr">
@@ -33919,7 +33919,7 @@
       </c>
       <c r="J743" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K743" s="2" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="J744" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K744" s="2" t="inlineStr">
@@ -34009,7 +34009,7 @@
       </c>
       <c r="J745" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K745" s="2" t="inlineStr">
@@ -34054,7 +34054,7 @@
       </c>
       <c r="J746" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K746" s="2" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="J747" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K747" s="2" t="inlineStr">
@@ -34144,7 +34144,7 @@
       </c>
       <c r="J748" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K748" s="2" t="inlineStr">
@@ -34189,7 +34189,7 @@
       </c>
       <c r="J749" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K749" s="2" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="J750" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K750" s="2" t="inlineStr">
@@ -34279,7 +34279,7 @@
       </c>
       <c r="J751" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K751" s="2" t="inlineStr">
@@ -34324,7 +34324,7 @@
       </c>
       <c r="J752" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K752" s="2" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="J753" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K753" s="2" t="inlineStr">
@@ -34414,7 +34414,7 @@
       </c>
       <c r="J754" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K754" s="2" t="inlineStr">
@@ -34459,7 +34459,7 @@
       </c>
       <c r="J755" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K755" s="2" t="inlineStr">
@@ -34504,7 +34504,7 @@
       </c>
       <c r="J756" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K756" s="2" t="inlineStr">
@@ -34549,7 +34549,7 @@
       </c>
       <c r="J757" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K757" s="2" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="J758" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K758" s="2" t="inlineStr">
@@ -34639,7 +34639,7 @@
       </c>
       <c r="J759" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K759" s="2" t="inlineStr">
@@ -34684,7 +34684,7 @@
       </c>
       <c r="J760" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K760" s="2" t="inlineStr">
@@ -34729,7 +34729,7 @@
       </c>
       <c r="J761" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K761" s="2" t="inlineStr">
@@ -34774,7 +34774,7 @@
       </c>
       <c r="J762" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K762" s="2" t="inlineStr">
@@ -34819,7 +34819,7 @@
       </c>
       <c r="J763" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K763" s="2" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="J764" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K764" s="2" t="inlineStr">
@@ -34909,7 +34909,7 @@
       </c>
       <c r="J765" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K765" s="2" t="inlineStr">
@@ -34954,7 +34954,7 @@
       </c>
       <c r="J766" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K766" s="2" t="inlineStr">
@@ -34999,7 +34999,7 @@
       </c>
       <c r="J767" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K767" s="2" t="inlineStr">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="J768" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K768" s="2" t="inlineStr">
@@ -35089,7 +35089,7 @@
       </c>
       <c r="J769" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K769" s="2" t="inlineStr">
@@ -35134,7 +35134,7 @@
       </c>
       <c r="J770" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K770" s="2" t="inlineStr">
@@ -35179,7 +35179,7 @@
       </c>
       <c r="J771" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K771" s="2" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="J772" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K772" s="2" t="inlineStr">
@@ -35269,7 +35269,7 @@
       </c>
       <c r="J773" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K773" s="2" t="inlineStr">
@@ -35314,7 +35314,7 @@
       </c>
       <c r="J774" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K774" s="2" t="inlineStr">
@@ -35359,7 +35359,7 @@
       </c>
       <c r="J775" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K775" s="2" t="inlineStr">
@@ -35404,7 +35404,7 @@
       </c>
       <c r="J776" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K776" s="2" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="J777" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K777" s="2" t="inlineStr">
@@ -35494,7 +35494,7 @@
       </c>
       <c r="J778" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K778" s="2" t="inlineStr">
@@ -35539,7 +35539,7 @@
       </c>
       <c r="J779" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K779" s="2" t="inlineStr">
@@ -35584,7 +35584,7 @@
       </c>
       <c r="J780" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K780" s="2" t="inlineStr">
@@ -35629,7 +35629,7 @@
       </c>
       <c r="J781" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K781" s="2" t="inlineStr">
@@ -35674,7 +35674,7 @@
       </c>
       <c r="J782" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K782" s="2" t="inlineStr">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="J783" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K783" s="2" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="J784" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K784" s="2" t="inlineStr">
@@ -35809,7 +35809,7 @@
       </c>
       <c r="J785" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K785" s="2" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="J786" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K786" s="2" t="inlineStr">
